--- a/ig/tru-exemples/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/ig/tru-exemples/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:26:02+00:00</t>
+    <t>2024-03-11T15:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/tru-exemples/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/ig/tru-exemples/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T15:09:21+00:00</t>
+    <t>2024-03-11T15:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
